--- a/구성종목(PDF)TIME컬처액티브_2026-03-25.xlsx
+++ b/구성종목(PDF)TIME컬처액티브_2026-03-25.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>종목코드</t>
   </si>
@@ -30,6 +30,216 @@
   </si>
   <si>
     <t>비중(%)</t>
+  </si>
+  <si>
+    <t>에이피알</t>
+  </si>
+  <si>
+    <t>98,550,000</t>
+  </si>
+  <si>
+    <t>하이브</t>
+  </si>
+  <si>
+    <t>91,350,000</t>
+  </si>
+  <si>
+    <t>올릭스</t>
+  </si>
+  <si>
+    <t>75,227,600</t>
+  </si>
+  <si>
+    <t>004170</t>
+  </si>
+  <si>
+    <t>신세계</t>
+  </si>
+  <si>
+    <t>67,400,000</t>
+  </si>
+  <si>
+    <t>휴젤</t>
+  </si>
+  <si>
+    <t>64,500,000</t>
+  </si>
+  <si>
+    <t>001040</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
+    <t>63,000,000</t>
+  </si>
+  <si>
+    <t>006730</t>
+  </si>
+  <si>
+    <t>서부T&amp;D</t>
+  </si>
+  <si>
+    <t>3,993</t>
+  </si>
+  <si>
+    <t>56,580,810</t>
+  </si>
+  <si>
+    <t>035900</t>
+  </si>
+  <si>
+    <t>JYP Ent.</t>
+  </si>
+  <si>
+    <t>51,568,600</t>
+  </si>
+  <si>
+    <t>와이지엔터테인먼트</t>
+  </si>
+  <si>
+    <t>50,613,700</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>48,581,326</t>
+  </si>
+  <si>
+    <t>023530</t>
+  </si>
+  <si>
+    <t>롯데쇼핑</t>
+  </si>
+  <si>
+    <t>44,520,000</t>
+  </si>
+  <si>
+    <t>펄어비스</t>
+  </si>
+  <si>
+    <t>40,160,000</t>
+  </si>
+  <si>
+    <t>제닉</t>
+  </si>
+  <si>
+    <t>1,467</t>
+  </si>
+  <si>
+    <t>38,875,500</t>
+  </si>
+  <si>
+    <t>041510</t>
+  </si>
+  <si>
+    <t>에스엠</t>
+  </si>
+  <si>
+    <t>37,453,400</t>
+  </si>
+  <si>
+    <t>엘앤씨바이오</t>
+  </si>
+  <si>
+    <t>37,000,000</t>
+  </si>
+  <si>
+    <t>아이티센글로벌</t>
+  </si>
+  <si>
+    <t>35,840,000</t>
+  </si>
+  <si>
+    <t>코스메카코리아</t>
+  </si>
+  <si>
+    <t>32,200,300</t>
+  </si>
+  <si>
+    <t>파마리서치</t>
+  </si>
+  <si>
+    <t>31,282,500</t>
+  </si>
+  <si>
+    <t>035760</t>
+  </si>
+  <si>
+    <t>CJ ENM</t>
+  </si>
+  <si>
+    <t>30,110,100</t>
+  </si>
+  <si>
+    <t>003230</t>
+  </si>
+  <si>
+    <t>삼양식품</t>
+  </si>
+  <si>
+    <t>24,320,000</t>
+  </si>
+  <si>
+    <t>스튜디오드래곤</t>
+  </si>
+  <si>
+    <t>19,429,200</t>
+  </si>
+  <si>
+    <t>GS피앤엘</t>
+  </si>
+  <si>
+    <t>18,520,000</t>
+  </si>
+  <si>
+    <t>042520</t>
+  </si>
+  <si>
+    <t>한스바이오메드</t>
+  </si>
+  <si>
+    <t>17,383,350</t>
+  </si>
+  <si>
+    <t>더핑크퐁컴퍼니</t>
+  </si>
+  <si>
+    <t>17,098,550</t>
+  </si>
+  <si>
+    <t>달바글로벌</t>
+  </si>
+  <si>
+    <t>15,590,000</t>
+  </si>
+  <si>
+    <t>081660</t>
+  </si>
+  <si>
+    <t>미스토홀딩스</t>
+  </si>
+  <si>
+    <t>12,702,200</t>
+  </si>
+  <si>
+    <t>로킷헬스케어</t>
+  </si>
+  <si>
+    <t>12,150,300</t>
+  </si>
+  <si>
+    <t>클래시스</t>
+  </si>
+  <si>
+    <t>10,760,000</t>
+  </si>
+  <si>
+    <t>그래피</t>
+  </si>
+  <si>
+    <t>9,457,050</t>
   </si>
 </sst>
 </file>
@@ -98,9 +308,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -402,7 +615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -429,6 +642,497 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" customHeight="1" ht="30">
+      <c r="A2" s="2">
+        <v>278470</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>300</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" customHeight="1" ht="30">
+      <c r="A3" s="2">
+        <v>352820</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>300</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>7.93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" customHeight="1" ht="30">
+      <c r="A4" s="2">
+        <v>226950</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>401</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="30">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>200</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customHeight="1" ht="30">
+      <c r="A6" s="2">
+        <v>145020</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>250</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customHeight="1" ht="30">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>300</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="30">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2">
+        <v>802</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="30">
+      <c r="A10" s="2">
+        <v>122870</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2">
+        <v>899</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="30">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2">
+        <v>400</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="30">
+      <c r="A13" s="2">
+        <v>263750</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2">
+        <v>800</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="30">
+      <c r="A14" s="2">
+        <v>123330</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="30">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2">
+        <v>401</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="30">
+      <c r="A16" s="2">
+        <v>290650</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2">
+        <v>500</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="30">
+      <c r="A17" s="2">
+        <v>124500</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2">
+        <v>700</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="30">
+      <c r="A18" s="2">
+        <v>241710</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2">
+        <v>401</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="30">
+      <c r="A19" s="2">
+        <v>214450</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2">
+        <v>97</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="30">
+      <c r="A20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="2">
+        <v>501</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="30">
+      <c r="A21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="30">
+      <c r="A22" s="2">
+        <v>253450</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2">
+        <v>504</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="30">
+      <c r="A23" s="2">
+        <v>499790</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="2">
+        <v>400</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="30">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="2">
+        <v>401</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="30">
+      <c r="A25" s="2">
+        <v>403850</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2">
+        <v>997</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="30">
+      <c r="A26" s="2">
+        <v>483650</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="2">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="2">
+        <v>301</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="30">
+      <c r="A28" s="2">
+        <v>376900</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2">
+        <v>101</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" customHeight="1" ht="30">
+      <c r="A29" s="2">
+        <v>214150</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2">
+        <v>200</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" customHeight="1" ht="30">
+      <c r="A30" s="2">
+        <v>318060</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="2">
+        <v>201</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
